--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260625.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260625.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>846,349</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>846,349</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>759,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>759,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,181,441</t>
+          <t>797,897</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>797,897</t>
+          <t>371,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>371,000</t>
+          <t>1,181,441</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>143,386</t>
+          <t>10,463,121</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>10,463,121</t>
+          <t>143,386</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>491,000</t>
+          <t>4,396,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,396,578</t>
+          <t>3,435,981</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,361,384</t>
+          <t>491,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3,435,981</t>
+          <t>1,361,384</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>794,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,895,956</t>
+          <t>794,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,170,076</t>
+          <t>4,895,956</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>1,170,076</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>287,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>287,000</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,540,400</t>
+          <t>384,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>384,000</t>
+          <t>315,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>315,000</t>
+          <t>1,540,400</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>168,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>1,735,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>168,000</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>1,735,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>331,000</t>
+          <t>671,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>671,000</t>
+          <t>331,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2239,6 +2239,24 @@
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>-256,683,562</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
